--- a/extracted_studies.xlsx
+++ b/extracted_studies.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF7"/>
+  <dimension ref="A1:BA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,372 +459,347 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>study_type</t>
+          <t>model_name</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>model_name</t>
+          <t>extraction_level</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>extraction_level</t>
+          <t>study_category</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>study_category</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>scale</t>
+          <t>countries</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>countries</t>
+          <t>nb_countries_covered</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>nb_countries_covered</t>
+          <t>power_pool</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>power_pool</t>
+          <t>study_objective</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>study_objective</t>
+          <t>key_result</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>key_result</t>
+          <t>time_horizon_start</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>time_horizon</t>
+          <t>time_horizon_end</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>time_horizon_start</t>
+          <t>approach</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>time_horizon_end</t>
+          <t>method</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>approach</t>
+          <t>mathematical_approach</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>hydro</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>mathematical_approach</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>hydro</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>biomass</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>nuclear</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>biomass</t>
+          <t>geothermal</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>nuclear</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>geothermal</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>fossil</t>
+          <t>coal</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>coal</t>
+          <t>open_source</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>other_technologies</t>
+          <t>frequency_of_use</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>sdg_7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>open_source</t>
+          <t>sdg_13</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>data_requirements</t>
+          <t>ndc_mention</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>frequency_of_use</t>
+          <t>agenda_2063</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>sdg_7</t>
+          <t>aisesa_theme</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>sdg_13</t>
+          <t>informal_economy</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>ndc_mention</t>
+          <t>biomass_charcoal</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>agenda_2063</t>
+          <t>clean_cooking</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>aisesa_theme</t>
+          <t>power_reliability</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>informal_economy</t>
+          <t>urbanization</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>biomass_charcoal</t>
+          <t>strengths</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>clean_cooking</t>
+          <t>weaknesses</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>power_reliability</t>
+          <t>authors_affiliation</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>urbanization</t>
+          <t>author_origin</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>strengths</t>
+          <t>local_ownership</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>weaknesses</t>
+          <t>institutional_users</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>authors_affiliation</t>
+          <t>grey_literature</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>author_origin</t>
+          <t>cost_of_capital</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>local_ownership</t>
+          <t>financing_modelling</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>institutional_users</t>
+          <t>financing_mechanism</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>grey_literature</t>
+          <t>link_doi</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>cost_of_capital</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>financing_modelling</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>financing_mechanism</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>link_doi</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
           <t>contact</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>other_references</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>_tmp_KENYA POWER SECTOR DEVELOPNET SCENARIOS – ANALYSIS USING LONG RANGE ENERGY ALTERNATIVE PLANNING SYSTEM.pdf</t>
+          <t>_tmp_Wartsila_Mozambique_FINAL.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KENYA POWER SECTOR DEVELOPNET SCENARIOS – ANALYSIS USING LONG RANGE ENERGY ALTERNATIVE PLANNING SYSTEM</t>
+          <t>PLANNING MOZAMBIQUE’S OPTIMAL POWER SYSTEM EXPANSION Assessing the role of renewables in reducing total system cost</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>D. W. Irungu et al.</t>
+          <t>Wallace Manyara</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>PLEXOS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LEAP</t>
+          <t>full</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>long_term_planning</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>long_term_planning</t>
+          <t>national</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>national</t>
+          <t>MZ</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>SAPP</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>EAPP</t>
+          <t>To model and compare low and high renewable energy scenarios to identify the optimal, most cost-effective power mix for Mozambique's electricity system expansion through 2032.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>To analyze three possible power development scenarios for Kenya's electricity sector through 2030, comparing their greenhouse gas emissions and cost implications.</t>
+          <t>A high renewables expansion strategy, supported by flexible gas generation and energy storage, provides superior savings in both total system costs and CO2 emissions. This approach is $84.7 million cheaper than a low renewables scenario through 2032.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>The renewable energy scenario is the most suitable and sustainable path for Kenya, offering the greatest greenhouse gas savings at a low cost, despite the government's reference plan being the cheapest option.</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>long_term</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>bottom-up</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>optimization</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>bottom-up</t>
+          <t>linear_programming</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>simulation</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -834,17 +809,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -859,52 +834,52 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>proprietary</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>gas turbine, medium speed diesel, cogeneration</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>proprietary</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>quantitative,monetary,aggregated,disaggregated</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cross_cutting</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -919,44 +894,52 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>cross_cutting</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>data-driven insights,cost-optimal,reliable,rapid energy transition,flexible</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>critical need to strengthen Mozambique’s power transmission capabilities,underdeveloped transmission and distribution network</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Wärtsilä Energy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Electricidade de Moçambique</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>Jomo Kenyatta University of Agriculture and Technology</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -965,132 +948,111 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>dirungu@jkuat.ac.ke</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>_tmp_energies-14-03338-v2.pdf</t>
+          <t>_tmp_1-s2.0-S0306261913007277-main.pdf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rural Electriﬁcation Pathways: An Implementation of LEAP and GIS Tools in Mali</t>
+          <t>Adding value with CLEWS – Modelling the energy system and its interdependencies for Mauritius</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>V Sessa et al.</t>
+          <t>M Welsch et al.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>LEAP</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LEAP</t>
+          <t>full</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>long_term_planning</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>rural_electrification</t>
+          <t>national</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>national</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>EAPP</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>WAPP</t>
+          <t>To demonstrate the value of an integrated modelling approach for energy policy by comparing results from a standard energy model with those from a model that includes interdependencies with water, land, and climate systems.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>To model rural electrification pathways for Mali using LEAP and GIS tools, identifying the requirements and most viable options to achieve complete electrification by 2050.</t>
+          <t>A standard energy model significantly overestimates the economic and environmental benefits of ethanol production in Mauritius. An integrated approach reveals that interdependencies with water and land systems, especially under climate change, can erase projected benefits and even lead to increased emissions.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Decentralized solar PV is the most economically viable option for electrifying remote rural areas, proving cheaper than grid extension. This advantage increases when the positive effects of electricity access on household income are considered.</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>long_term</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>bottom-up</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>optimization</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>bottom-up</t>
+          <t>linear_programming</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>linear_programming</t>
+          <t>no</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1105,17 +1067,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1130,47 +1092,47 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>full_energy</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>proprietary</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>full_energy</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>quantitative,monetary,aggregated,disaggregated</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cross_cutting</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1185,278 +1147,197 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>powering_livelihoods</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>integrated approach,consistent strategies</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>high effort,coordination challenges</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>KTH Royal Institute of Technology,International Institute for Applied Systems Analysis,Stockholm Environment Institute – US Centre,Agricultural Research &amp; Extension Unit,Columbia University,International Atomic Energy Agency,International Renewable Energy Agency,United Nations Department of Economic and Social Affairs,Food and Agriculture Organization of the United Nations,Institute for Advanced Sustainability Studies</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>SE,AT,US,MU,DE,IT</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>LEAP facilitates scenario interaction, QGIS enables geographical component, considers electricity-income effects</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>centralized generation provenance not considered, no demonstration site, uncertain income effect timeline, lack of countrywide data for biogas</t>
+          <t>Government of Mauritius</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>Institute for Technology and Resources Management in the Tropics and Subtropics, TH Köln (University of Applied Sciences), Faculty of Sciences and Techniques of the University of Sciences, Techniques and Technologies of Bamako, USTT-B (FAST)</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>DE,ML</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>http://dx.doi.org/10.1016/j.apenergy.2013.08.083</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>pay-as-you-go financing</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/en14113338</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>vittorio.sessa@th-koeln.de</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>https://leap.sei.org/, https://qgis.org/en/site/</t>
+          <t>manuel.welsch@energy.kth.se</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>_tmp_1-s2.0-S0301421510007603-main.pdf</t>
+          <t>_tmp_VanZyletal2018CostofSouthAfricafairshareofGHGmitigation (3).pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The renewable energy targets of the Maghreb countries: Impact on electricity supply and conventional power markets</t>
+          <t>The cost of achieving South Africa’s ‘fair share’ of global climate change mitigation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bernhard Brand et al.</t>
+          <t>Hugo Van Zyl et al.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>Climate Equity Reference Calculator</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIME</t>
+          <t>light</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>long_term_planning</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>long_term_planning</t>
+          <t>national</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>regional</t>
+          <t>ZA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MA,DZ,TN,ES,PT,IT,FR,CH</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>SAPP</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>COMELEC</t>
+          <t>To estimate the emissions reduction pathways and associated economy-wide net costs or savings for South Africa to achieve its 'fair share' of global climate mitigation.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>To simulate the impact of renewable energy targets in Morocco, Algeria, and Tunisia on their conventional power generation systems and overall system costs until 2025.</t>
+          <t>South Africa can achieve its 'fair share' of global mitigation with significant net savings, which are maximized by making greater use of renewable energy options.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Achieving the renewable energy targets creates savings in the conventional power system, primarily from avoided fuel costs. For every euro spent on renewables, Tunisia saves €0.27, while Morocco and Algeria save only €0.17 and €0.15, respectively.</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>long_term</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>bottom-up</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>optimization</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>linear_programming</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>full_energy</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>liquid fuel (oil) power plants, open cycle gas turbines (OC), combined-cycle gas-fired power stations (CC), hydro-storage plants, pumped storage hydropower plants</t>
-        </is>
-      </c>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>proprietary</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>quantitative,monetary,aggregated,disaggregated</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cross_cutting</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1471,7 +1352,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>cross_cutting</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1479,182 +1360,129 @@
           <t>no</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>renewable energies are able to replace an important part of fossil generation</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>cost input parameters do not include risk primes or safety and security expenses related to the risk of political instability and terrorism</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>Institute of Energy Economics at the University of Cologne</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>https://doi.org/10.1080/14693062.2018.1437019</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>doi:10.1016/j.enpol.2010.10.010</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>brandb@uni-koeln.de</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr"/>
+          <t>hugo@independentecon.co.za</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>_tmp_Moksnes_2017_Environ._Res._Lett._12_095008.pdf</t>
+          <t>_tmp_1-s2.0-S1755008418300565-main.pdf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Electrification pathways for Kenya–linking spatial electrification analysis and medium to long term energy planning</t>
+          <t>Pathways for low carbon Nigeria in 2050 by using NECAL2050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nandi Moksnes et al.</t>
+          <t>Michael O. Dioha et al.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>NECAL2050</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>OnSSET, OSeMOSYS</t>
+          <t>full</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>long_term_planning</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>rural_electrification</t>
+          <t>national</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>national</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>WAPP</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>EAPP</t>
+          <t>To examine and compare the energy balances and greenhouse gas mitigation potentials of four alternative low-carbon development scenarios for Nigeria by 2050.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>To analyze and optimize electrification pathways for Kenya to 2030 by linking a geospatial model for off-grid supply with a long-term energy model for grid supply under different demand scenarios.</t>
+          <t>Alternative low-carbon pathways reduce energy consumption and emissions compared to the business-as-usual case, but fossil fuels will still dominate Nigeria's energy system in all scenarios by 2050.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>In a low-demand scenario, stand-alone systems are the least-cost option for about half the population to gain electricity access, while higher demand levels make grid extension and mini-grids more economically viable.</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>long_term</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>bottom-up</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>bottom-up</t>
+          <t>other</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>linear_programming</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1674,7 +1502,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1684,7 +1512,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1694,38 +1522,42 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>full_energy</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>quantitative,monetary,aggregated,disaggregated</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cross_cutting</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1735,62 +1567,62 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>powering_livelihoods</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>transparent and open source model, Nigeria-specific data, accurate assumptions, high quality data, technically/practically attainable results</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>uncertainties, aggregation of key sectors, economic indices projections, not flexible, no macroeconomic implications, no cost levels</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>TERI School of Advanced Studies, James Cook University, Federal University of Technology, Owerri</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>IN,AU,NG</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>utilization of the strengths of both tools, optimal split between off-grid and grid electricity system</t>
-        </is>
-      </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>grid demand underestimated, only one iteration between models, OnSSET assumes overnight electrification, time resolution in OnSSET</t>
+          <t>Energy Commission of Nigeria</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>KTH Royal Institute of Technology</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1801,130 +1633,117 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>https://doi.org/10.1016/j.ref.2019.02.004</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.8%</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1088/1748-9326/aa7e18</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>nandi@kth.se</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr"/>
+          <t>michael.dioha@terisas.ac.in</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>_tmp_1-s2.0-S2211467X24000191-main.pdf</t>
+          <t>_tmp_energies-14-06258-v2.pdf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mid- to long-term capacity planning for a reliable power system in Kenya</t>
+          <t>Modeling Long-Term Electricity Generation Planning to Reduce Carbon Dioxide Emissions in Nigeria</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mungai Kihara et al.</t>
+          <t>Juyoul Kim et al.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>article</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>MESSAGE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>long_term_planning</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>long_term_planning</t>
+          <t>national</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>national</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>WAPP</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>EAPP</t>
+          <t>To model alternative long-term electricity supply mixes for Nigeria to meet future demand and reduce CO2 emissions, while also estimating the environmental impacts and damage costs of different generation technologies.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>To assess how Kenya can meet growing electricity demand with a predominantly renewable system by applying a novel framework that links a capacity expansion model (OSeMOSYS) with a production cost model (FlexTool).</t>
+          <t>Without CO2 emission limits, oil and gas power plants are the optimal choice to meet Nigeria's future energy needs. When CO2 restrictions are applied, nuclear power plants become the best option, having the lowest environmental damage costs.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Kenya is well-positioned to maintain its very low-carbon power system while meeting future demand growth by leveraging its significant geothermal and wind resources. Geothermal provides firm generation that complements a large expansion of variable wind capacity.</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>long_term</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>bottom-up</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>bottom-up</t>
+          <t>mixed-integer_programming</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>linear_programming</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1934,7 +1753,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1944,7 +1763,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1954,62 +1773,62 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>proprietary</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>batteries,pumped hydro</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>quantitative,monetary,aggregated,disaggregated</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cross_cutting</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2019,7 +1838,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>cross_cutting</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2029,103 +1848,74 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>low greenhouse gas emissions,baseload power,consistent and massive output,reliable source of energy</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>nuclear accidents,management of radioactive waste,radiophobia,inconsistent wind,solar intermittency</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Department of NPP Engineering, KEPCO International Nuclear Graduate School</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>novel framework,effectiveness of the methodology,well placed to maintain very low carbon generation system</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>limitations of CEMs in representation of VRE,CEM undervalues flexibility requirements,CEM overestimates baseload technologies</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>Ministry of Energy and Petroleum, UCL Energy Institute, Imperial College London, Kenya Power and Lighting Company Plc., Energy and Petroleum Regulatory Authority, Transition Zero, UCL Institute for Sustainable Resources</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>KE,GB</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Ministry of Energy and Petroleum, Kenya Power and Lighting Company Plc., Energy and Petroleum Regulatory Authority</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>https://doi.org/10.3390/en14196258</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.9%</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.esr.2024.101312</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>p.lubello@ucl.ac.uk</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>http://doi.org/10.5281/zenodo.8337794</t>
+          <t>jykim@kings.ac.kr</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>_tmp_Carvallo-Shaw-Avila-Kammen-EST-SWITCHKenya-2017.pdf</t>
+          <t>_tmp_1-s2.0-S1364032116306281-main.pdf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sustainable Low-Carbon Expansion for the Power Sector of an Emerging Economy: The Case of Kenya</t>
+          <t>Energy policy for low carbon development in Nigeria: A LEAP model application</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Juan-Pablo Carvallo et al.</t>
+          <t>Nnaemeka Vincent Emodi et al.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2135,82 +1925,82 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>LEAP</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>full</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>long_term_planning</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>long_term_planning</t>
+          <t>national</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>national</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>WAPP</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>EAPP</t>
+          <t>To model Nigeria's future energy demand, supply, and associated GHG emissions from 2010 to 2040 under four different policy scenarios.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>To explore low-carbon development pathways for the Kenyan power sector by modeling its expansion under various scenarios of load growth, technology costs, and environmental policies.</t>
+          <t>Aggressive policy interventions, as modelled in the Green Optimistic (GO) scenario, would significantly reduce Nigeria's projected 2040 energy demand and GHG emissions compared to the reference scenario.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Kenya's power system can transition to a low-carbon future dominated by geothermal and wind power. A cost-effective expansion requires storage, diesel engines, and transmission upgrades to provide flexibility for high wind penetration.</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>long_term</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>bottom-up</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>simulation</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>bottom-up</t>
+          <t>other</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>optimization</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>mixed-integer_programming</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -2230,17 +2020,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2250,107 +2040,103 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>full_energy</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>proprietary</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>battery storage</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>quantitative,monetary,aggregated,disaggregated</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cross_cutting</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>cross_cutting</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>flexible data structure,easy to use,rich in technical and end-user details,provides electricity generation alternatives with lower GHG emissions</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>excluded railway, airway, and seaway transport system due to lack of available data,alternative scenarios do not exhaust possibilities,does not consider ability of consumers to pay for energy services,does not explore effect of energy pricing,high cost of renewable energy,high capital investment for renewable energy</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>College of Business, Law and Governance, James Cook University,Department of Computer Science, College of Physical and Applied Science, Michael Okpara University of Agriculture,Department of Finance, IBS Hyderabad, IFHE University,Faculty of Law, Abia State University</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>AU,NG,IN</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>unprecedented spatial and temporal resolution, system-level modeling, analytical approach</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>lack of high resolution temporal data for hydropower, coarse estimation for load projections, omissions of intra-annual heterogeneity, simplifications of the model and data</t>
-        </is>
-      </c>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>Renewable and Appropriate Energy Laboratory, University of California, Berkeley, Energy and Resources Group, University of California, Berkeley, Goldman School of Public Policy, University of California, Berkeley</t>
+          <t>no</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2361,31 +2147,685 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>http://dx.doi.org/10.1016/j.rser.2016.09.118</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>10.1021/acs.est.7b00345</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>kammen@berkeley.edu</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr"/>
+          <t>nnaemeka.emodi@my.jcu.edu.au</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>_tmp_energies-15-05083-v2.pdf</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Modeling the Next Decade of Energy Sustainability: A Case of a Developing Country</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>T Adeyemi-Kayode et al.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LEAP</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>long_term_planning</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>national</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>WAPP</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>To model and assess future energy scenarios for Nigeria using multi-criteria decision analysis to identify a sustainable generation mix based on technical, social, economic, and environmental factors.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>A scenario combining renewables, natural gas, and biomass (RNB) is the best option for meeting Nigeria's future energy demand while reducing greenhouse gas emissions and costs.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>bottom-up</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>simulation</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>proprietary</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>ad_hoc</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>cross_cutting</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>Department of Electrical and Information Engineering, Covenant University, Ota 112104, Ogun State, Nigeria; Department of Computer Science and Communication, Østfold University College, 1757 Halden, Norway</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>NG,NO</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/en15145083</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>sanjay.misra@hiof.no</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>_tmp_1-s2.0-S2210670721000445-main.pdf</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Low emissions analysis platform model for renewable energy: Community-scale case studies in Nigeria</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>B. Ugwoke et al.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LEAP</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>rural_electrification</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>subnational</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>WAPP</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>To perform community-scale energy planning for two rural Nigerian communities from 2015 to 2040, investigating the implications of transforming them to a sustainable, renewable-based energy supply under different demand-side management scenarios.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Integrating demand-side management strategies with renewable energy supply provides clear benefits, significantly reducing energy demand and greenhouse gas emissions. The scenario combining advanced building retrofits with specific indoor environmental quality standards delivered the best performance and largest reduction in energy expenditures.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>optimization</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>linear_programming</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>proprietary</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>powering_livelihoods</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>useful insights for design and implementation of localised energy policies, concurrently define and reach multiple targets, goals and impacts</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>no integrative scenario for grid connection, no time-of-day pricing, no economic optimum for interruptions, cooking energy use excluded</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Energy Center Lab, Department of Energy Politecnico di Torino, Department of Materials Science &amp; Engineering and Department of Electrical &amp; Computer Engineering, Michigan Technological University, Department of Electronics and Nanoengineering, School of Electrical Engineering, Aalto University</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>IT,US,FI</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.scs.2021.102750</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>blessing.ugwoke@polito.it</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>_tmp_20260601145246574409__tmp_1-s2.0-S0196890424012378-main.pdf</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>An integrated geospatial techno-economic multi-scenario mapping assessment of PV-based green hydrogen development opportunities: A vision to support its deployment in Morocco</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>F.-z. Ouchani et al.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PVH2-MSTEA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>geospatial</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>national</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>COMELEC</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>To identify the most cost-effective sites in Morocco for producing green hydrogen from solar PV, using a geospatial techno-economic model that considers multiple scenarios for energy and hydrogen transport.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Approximately 66% of Morocco's territory is suitable for PV-based green hydrogen projects, with the most cost-effective strategy being the transmission of solar electricity from high-yield inland sites to coastal production facilities. This approach can yield hydrogen at a competitive cost of around $2.15/kg.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>cross_cutting</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.enconman.2024.119296</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>ouchani@greenenergypark.ma</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2398,7 +2838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2420,11 +2860,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LEAP</t>
+          <t>PLEXOS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2435,7 +2875,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2450,71 +2890,71 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QGIS</t>
+          <t>AEZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>geospatial_electrification</t>
+          <t>production_cost</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DIME</t>
+          <t>WEAP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>capacity_expansion</t>
+          <t>demand_forecast</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OnSSET</t>
+          <t>Climate Equity Reference Calculator</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>geospatial_electrification</t>
+          <t>economic</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OSeMOSYS</t>
+          <t>NECAL2050</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>capacity_expansion</t>
+          <t>demand_forecast</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OSeMOSYS</t>
+          <t>MESSAGE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2525,26 +2965,26 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FlexTool</t>
+          <t>SIMPACTS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>production_cost</t>
+          <t>simulation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>LEAP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2555,14 +2995,78 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAM</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>LEAP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>capacity_expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LEAP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>capacity_expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>43</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GIS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>geospatial_electrification</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>43</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ArcGIS Pro</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>geospatial_electrification</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>43</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pvlib Python software</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hybrid_optimization</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2575,7 +3079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2592,131 +3096,91 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>MZ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>MU</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ZA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>KE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>KE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>KE</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -2731,7 +3195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2748,61 +3212,91 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EAPP</t>
+          <t>SAPP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WAPP</t>
+          <t>EAPP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COMELEC</t>
+          <t>SAPP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EAPP</t>
+          <t>WAPP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EAPP</t>
+          <t>WAPP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EAPP</t>
+          <t>WAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>WAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WAPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>COMELEC</t>
         </is>
       </c>
     </row>
